--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -351,25 +351,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>**Characteristic**</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>**N = 23,386**</t>
+          <t>N = 23,386</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Age at fracture occurrence</t>
+          <t>Age at Fracture Occurrence</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -381,7 +381,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fracture site</t>
+          <t>Fracture Site</t>
         </is>
       </c>
     </row>
@@ -431,36 +431,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cancer</t>
+          <t>Max of 730 days from index date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>745 (3.2%)</t>
+          <t>15,411 (66%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cancer, Fracture ensuing incident (index) fracture</t>
+          <t>Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2 (&lt;0.1%)</t>
+          <t>4,036 (17%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cancer, Paget’s disease of the bone, or other metabolic bone diseases</t>
+          <t>End of data collection period</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>1,838 (7.9%)</t>
         </is>
       </c>
     </row>
@@ -479,31 +479,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>End of data collection period</t>
+          <t>Cancer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1,838 (7.9%)</t>
+          <t>745 (3.2%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>End of data collection period, Cancer</t>
+          <t>Paget’s disease of the bone, or other metabolic bone diseases</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>78 (0.3%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
+          <t>Cancer, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -515,31 +515,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fracture ensuing incident (index) fracture</t>
+          <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4,036 (17%)</t>
+          <t>2 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date</t>
+          <t>Max of 730 days from index date, End of data collection period</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15,411 (66%)</t>
+          <t>2 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, Cancer</t>
+          <t>Cancer, Paget’s disease of the bone, or other metabolic bone diseases</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -551,19 +551,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, End of data collection period</t>
+          <t>End of data collection period, Cancer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2 (&lt;0.1%)</t>
+          <t>1 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, Fracture ensuing incident (index) fracture</t>
+          <t>Max of 730 days from index date, Cancer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, Paget’s disease of the bone, or other metabolic bone diseases</t>
+          <t>Max of 730 days from index date, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -587,12 +587,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paget’s disease of the bone, or other metabolic bone diseases</t>
+          <t>Max of 730 days from index date, Paget’s disease of the bone, or other metabolic bone diseases</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>78 (0.3%)</t>
+          <t>1 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
@@ -617,6 +617,68 @@
       <c r="B23" t="inlineStr">
         <is>
           <t>730 (365, 730)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>User Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non-User</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1,014 (4.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>22,372 (96%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non-user Visit Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>No Visits</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>132 (13%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Visits with Non-clinically Relevant Staff</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>882 (87%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,7 +362,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>N = 23,386</t>
+          <t>N = 23,957</t>
         </is>
       </c>
     </row>
@@ -393,7 +393,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3,173 (14%)</t>
+          <t>3,118 (13%)</t>
         </is>
       </c>
     </row>
@@ -405,7 +405,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1,682 (7.2%)</t>
+          <t>1,707 (7.1%)</t>
         </is>
       </c>
     </row>
@@ -417,7 +417,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18,531 (79%)</t>
+          <t>19,132 (80%)</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15,411 (66%)</t>
+          <t>16,341 (68%)</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4,036 (17%)</t>
+          <t>3,859 (16%)</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1,838 (7.9%)</t>
+          <t>1,868 (7.8%)</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,266 (5.4%)</t>
+          <t>1,356 (5.7%)</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>745 (3.2%)</t>
+          <t>462 (1.9%)</t>
         </is>
       </c>
     </row>
@@ -496,14 +496,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>78 (0.3%)</t>
+          <t>64 (0.3%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cancer, Fracture ensuing incident (index) fracture</t>
+          <t>Max of 730 days from index date, End of data collection period</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -515,31 +515,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
+          <t>Cancer, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2 (&lt;0.1%)</t>
+          <t>1 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, End of data collection period</t>
+          <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2 (&lt;0.1%)</t>
+          <t>1 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cancer, Paget’s disease of the bone, or other metabolic bone diseases</t>
+          <t>Max of 730 days from index date, Cancer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>End of data collection period, Cancer</t>
+          <t>Max of 730 days from index date, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, Cancer</t>
+          <t>Max of 730 days from index date, Paget’s disease of the bone, or other metabolic bone diseases</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -575,110 +575,74 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, Fracture ensuing incident (index) fracture</t>
+          <t>Follow up time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>730 (452, 730)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, Paget’s disease of the bone, or other metabolic bone diseases</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>User Status</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Paget’s disease of the bone, or other metabolic bone diseases, Fracture ensuing incident (index) fracture</t>
+          <t>Non-User</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>800 (3.3%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Follow up time</t>
+          <t>User</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>730 (365, 730)</t>
+          <t>23,157 (97%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>User Status</t>
+          <t>Non-user Visit Status</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Non-User</t>
+          <t>No Visits</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1,014 (4.3%)</t>
+          <t>101 (13%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Visits with Non-clinically Relevant Staff</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22,372 (96%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Non-user Visit Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>No Visits</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>132 (13%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Visits with Non-clinically Relevant Staff</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>882 (87%)</t>
+          <t>699 (87%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -587,7 +587,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>User Status</t>
+          <t>Heathcare Service User Status</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Non-user Visit Status</t>
+          <t>Heathcare Service Non-user Visit Status</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -424,7 +424,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Censoring event</t>
+          <t>Censoring Event</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -625,24 +625,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>No Visits</t>
+          <t>Visits with Non-clinically Relevant Staff</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>101 (13%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Visits with Non-clinically Relevant Staff</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>699 (87%)</t>
+          <t>800 (100%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>800 (3.3%)</t>
+          <t>824 (3.4%)</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23,157 (97%)</t>
+          <t>23,133 (97%)</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>800 (100%)</t>
+          <t>824 (100%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>824 (3.4%)</t>
+          <t>732 (3.1%)</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23,133 (97%)</t>
+          <t>23,225 (97%)</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>824 (100%)</t>
+          <t>732 (100%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -362,7 +362,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>N = 23,957</t>
+          <t>N = 23,956</t>
         </is>
       </c>
     </row>
@@ -417,7 +417,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19,132 (80%)</t>
+          <t>19,131 (80%)</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16,341 (68%)</t>
+          <t>16,340 (68%)</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23,225 (97%)</t>
+          <t>23,224 (97%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,7 +362,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>N = 23,956</t>
+          <t>N = 17,705</t>
         </is>
       </c>
     </row>
@@ -374,7 +374,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>70 (61, 81)</t>
+          <t>71 (61, 81)</t>
         </is>
       </c>
     </row>
@@ -393,7 +393,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3,118 (13%)</t>
+          <t>2,452 (14%)</t>
         </is>
       </c>
     </row>
@@ -405,7 +405,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1,707 (7.1%)</t>
+          <t>1,334 (7.5%)</t>
         </is>
       </c>
     </row>
@@ -417,7 +417,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19,131 (80%)</t>
+          <t>13,919 (79%)</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16,340 (68%)</t>
+          <t>11,044 (62%)</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3,859 (16%)</t>
+          <t>3,958 (22%)</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1,868 (7.8%)</t>
+          <t>1,331 (7.5%)</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,356 (5.7%)</t>
+          <t>1,015 (5.7%)</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>462 (1.9%)</t>
+          <t>311 (1.8%)</t>
         </is>
       </c>
     </row>
@@ -496,26 +496,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>64 (0.3%)</t>
+          <t>43 (0.2%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, End of data collection period</t>
+          <t>Cancer, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2 (&lt;0.1%)</t>
+          <t>1 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cancer, Fracture ensuing incident (index) fracture</t>
+          <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
+          <t>Max of 730 days from index date, End of data collection period</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -539,98 +539,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, Cancer</t>
+          <t>Follow up time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>730 (231, 730)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, Fracture ensuing incident (index) fracture</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>Heathcare Service User Status</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, Paget’s disease of the bone, or other metabolic bone diseases</t>
+          <t>Non-User</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>727 (4.1%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Follow up time</t>
+          <t>User</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>730 (452, 730)</t>
+          <t>16,978 (96%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Heathcare Service User Status</t>
+          <t>Heathcare Service Non-user Visit Status</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Non-User</t>
+          <t>Visits with Non-clinically Relevant Staff</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>732 (3.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>23,224 (97%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Heathcare Service Non-user Visit Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Visits with Non-clinically Relevant Staff</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>732 (100%)</t>
+          <t>727 (100%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,81 +362,81 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>N = 17,705</t>
+          <t>N = 22,900</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Age at Fracture Occurrence</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>71 (61, 81)</t>
+          <t>Fracture Site</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fracture Site</t>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3,197 (14%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hip</t>
+          <t>Vertebra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2,452 (14%)</t>
+          <t>1,699 (7.4%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vertebra</t>
+          <t>NHNV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1,334 (7.5%)</t>
+          <t>18,004 (79%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NHNV</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>13,919 (79%)</t>
+          <t>Censoring Event</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Censoring Event</t>
+          <t>Max of 730 days from index date</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9,730 (42%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date</t>
+          <t>End of Study</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11,044 (62%)</t>
+          <t>6,026 (26%)</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3,958 (22%)</t>
+          <t>4,071 (18%)</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1,331 (7.5%)</t>
+          <t>1,479 (6.5%)</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,015 (5.7%)</t>
+          <t>1,150 (5.0%)</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>311 (1.8%)</t>
+          <t>379 (1.7%)</t>
         </is>
       </c>
     </row>
@@ -496,26 +496,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>43 (0.2%)</t>
+          <t>54 (0.2%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cancer, Fracture ensuing incident (index) fracture</t>
+          <t>Max of 730 days from index date, End of Study</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>7 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
+          <t>Cancer, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, End of data collection period</t>
+          <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -539,62 +539,86 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Follow up time</t>
+          <t>Fracture ensuing incident (index) fracture, End of Study</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>730 (231, 730)</t>
+          <t>1 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Heathcare Service User Status</t>
+          <t>Max of 730 days from index date, Fracture ensuing incident (index) fracture</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Non-User</t>
+          <t>Follow up time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>727 (4.1%)</t>
+          <t>578 (192, 730)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>16,978 (96%)</t>
+          <t>Heathcare Service User Status</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Heathcare Service Non-user Visit Status</t>
+          <t>Non-User</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>621 (2.7%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>22,279 (97%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Heathcare Service Non-user Visit Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Visits with Non-clinically Relevant Staff</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>727 (100%)</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>621 (100%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -587,7 +587,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>621 (2.7%)</t>
+          <t>599 (2.6%)</t>
         </is>
       </c>
     </row>
@@ -599,26 +599,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22,279 (97%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Heathcare Service Non-user Visit Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Visits with Non-clinically Relevant Staff</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>621 (100%)</t>
+          <t>22,301 (97%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Table1_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -587,7 +587,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>599 (2.6%)</t>
+          <t>621 (2.7%)</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22,301 (97%)</t>
+          <t>22,279 (97%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Heathcare Service Non-user Visit Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Visits with Non-clinically Relevant Staff</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>621 (100%)</t>
         </is>
       </c>
     </row>
